--- a/data/trans_orig/P37B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023</t>
+          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023 (tasa de respuesta: 97,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>30826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37811</t>
+          <t>38006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35119</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>62437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,42 +898,42 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6845</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27727</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>357077</t>
+          <t>356336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>383319</t>
+          <t>382445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>331952</t>
+          <t>333224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>357924</t>
+          <t>357980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>698750</t>
+          <t>699380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>736329</t>
+          <t>734647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30745</t>
+          <t>31812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39988</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40045</t>
+          <t>40660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63453</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76701</t>
+          <t>80594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>609282</t>
+          <t>608896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41408</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>64870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129132</t>
+          <t>128576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>807112</t>
+          <t>795191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63840</t>
+          <t>59961</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73330</t>
+          <t>73491</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267268</t>
+          <t>264806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>739462</t>
+          <t>735007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>454571</t>
+          <t>454778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>487529</t>
+          <t>488527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>608306</t>
+          <t>629513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1207688</t>
+          <t>1209327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>19202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67625</t>
+          <t>66924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45149</t>
+          <t>45479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69305</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54240</t>
+          <t>61661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128384</t>
+          <t>127423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>68937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115554</t>
+          <t>111749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61881</t>
+          <t>62817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100475</t>
+          <t>101392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146650</t>
+          <t>142863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204341</t>
+          <t>201042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,47 +2257,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>13154</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>7780</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>12788</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>37349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>291237</t>
+          <t>291007</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>341840</t>
+          <t>341663</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>330073</t>
+          <t>329162</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>382800</t>
+          <t>380293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>633672</t>
+          <t>633277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>707478</t>
+          <t>705356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35255</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70319</t>
+          <t>69476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54373</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95331</t>
+          <t>95575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27353</t>
+          <t>26753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51949</t>
+          <t>53461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35348</t>
+          <t>34169</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64899</t>
+          <t>64836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72134</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108000</t>
+          <t>106547</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65941</t>
+          <t>64800</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>434127</t>
+          <t>432470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>473850</t>
+          <t>476195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>508559</t>
+          <t>508628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>574541</t>
+          <t>575576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>958037</t>
+          <t>957044</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1034520</t>
+          <t>1040178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39802</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69838</t>
+          <t>70395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47465</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85871</t>
+          <t>84548</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98705</t>
+          <t>92757</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146393</t>
+          <t>142538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>225787</t>
+          <t>224683</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>937615</t>
+          <t>1024458</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>181719</t>
+          <t>184339</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>240820</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>433020</t>
+          <t>427884</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1522990</t>
+          <t>1330652</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52446</t>
+          <t>50834</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105609</t>
+          <t>104547</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>79494</t>
+          <t>78916</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,47 +3734,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>132178</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>103950</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>166601</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>132178</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>104605</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>166943</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1251894</t>
+          <t>1187141</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1884026</t>
+          <t>1884601</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1662265</t>
+          <t>1665455</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1759985</t>
+          <t>1756033</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2675225</t>
+          <t>2806577</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3598678</t>
+          <t>3599820</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>114282</t>
+          <t>116058</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>201449</t>
+          <t>201349</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>154141</t>
+          <t>152412</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>203696</t>
+          <t>203517</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>287247</t>
+          <t>284619</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>393770</t>
+          <t>390844</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>36858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26813</t>
+          <t>29731</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46441</t>
+          <t>54710</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62437</t>
+          <t>70509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>22655</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>32659</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>371710</t>
+          <t>396650</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>356336</t>
+          <t>380278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>382445</t>
+          <t>409787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>346535</t>
+          <t>378997</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>333224</t>
+          <t>364525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>357980</t>
+          <t>391649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>718245</t>
+          <t>775647</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>699380</t>
+          <t>754570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>734647</t>
+          <t>795390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>31587</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>32333</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>23875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>41990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>51463</t>
+          <t>53293</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40660</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64793</t>
+          <t>66007</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422826</t>
+          <t>457161</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422826</t>
+          <t>457161</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422826</t>
+          <t>457161</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>414758</t>
+          <t>452363</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>414758</t>
+          <t>452363</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>414758</t>
+          <t>452363</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>837584</t>
+          <t>909524</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>837584</t>
+          <t>909524</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>837584</t>
+          <t>909524</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>308557</t>
+          <t>65797</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80594</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>608896</t>
+          <t>87992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51941</t>
+          <t>55943</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64870</t>
+          <t>68721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>360497</t>
+          <t>121739</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128576</t>
+          <t>101025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>795191</t>
+          <t>146179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>31457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59961</t>
+          <t>45666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>42619</t>
+          <t>43781</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73491</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>532505</t>
+          <t>599599</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264806</t>
+          <t>573242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>735007</t>
+          <t>626302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>471075</t>
+          <t>531279</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>454778</t>
+          <t>512213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>488527</t>
+          <t>548794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1003579</t>
+          <t>1130878</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>629513</t>
+          <t>1100031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1209327</t>
+          <t>1162388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>47147</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>34529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66924</t>
+          <t>67193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>4,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57441</t>
+          <t>63299</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70362</t>
+          <t>77895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>99602</t>
+          <t>110446</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61661</t>
+          <t>93616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127423</t>
+          <t>131355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>917379</t>
+          <t>750215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>917379</t>
+          <t>750215</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>917379</t>
+          <t>750215</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>598020</t>
+          <t>670159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>598020</t>
+          <t>670159</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>598020</t>
+          <t>670159</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1515399</t>
+          <t>1420374</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1515399</t>
+          <t>1420374</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1515399</t>
+          <t>1420374</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89690</t>
+          <t>100136</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68937</t>
+          <t>77558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111749</t>
+          <t>124144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>82423</t>
+          <t>97314</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62817</t>
+          <t>81704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101392</t>
+          <t>113586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>172114</t>
+          <t>197450</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>142863</t>
+          <t>168226</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201042</t>
+          <t>226907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,27 +2350,27 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37349</t>
+          <t>46949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>317477</t>
+          <t>366924</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>291007</t>
+          <t>340685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>341663</t>
+          <t>393606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>351384</t>
+          <t>374420</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>329162</t>
+          <t>354318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>380293</t>
+          <t>394827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>668861</t>
+          <t>741343</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>633277</t>
+          <t>710822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>705356</t>
+          <t>781218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>49447</t>
+          <t>51833</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34445</t>
+          <t>36668</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69476</t>
+          <t>71684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23144</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72591</t>
+          <t>79192</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>61938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95575</t>
+          <t>101938</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>466824</t>
+          <t>537395</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>466824</t>
+          <t>537395</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>466824</t>
+          <t>537395</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>480732</t>
+          <t>527981</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>480732</t>
+          <t>527981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>480732</t>
+          <t>527981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>947556</t>
+          <t>1065376</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>947556</t>
+          <t>1065376</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>947556</t>
+          <t>1065376</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>38283</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53461</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50380</t>
+          <t>59715</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>47685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64836</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>88663</t>
+          <t>102123</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70177</t>
+          <t>84182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106547</t>
+          <t>123210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,22 +2954,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>24816</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43765</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>42722</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31382</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64800</t>
+          <t>56201</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>454860</t>
+          <t>493282</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>432470</t>
+          <t>465860</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>476195</t>
+          <t>511648</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>536221</t>
+          <t>518553</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>508628</t>
+          <t>496981</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>575576</t>
+          <t>536269</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>991082</t>
+          <t>1011835</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>957044</t>
+          <t>982491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1040178</t>
+          <t>1038993</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>53160</t>
+          <t>55088</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>41876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70395</t>
+          <t>73630</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>67185</t>
+          <t>75534</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>60612</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84548</t>
+          <t>93411</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>120345</t>
+          <t>130622</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92757</t>
+          <t>109821</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>142538</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>571557</t>
+          <t>617755</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>571557</t>
+          <t>617755</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>571557</t>
+          <t>617755</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>679551</t>
+          <t>675618</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>679551</t>
+          <t>675618</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>679551</t>
+          <t>675618</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1251109</t>
+          <t>1293373</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1251109</t>
+          <t>1293373</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1251109</t>
+          <t>1293373</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>456159</t>
+          <t>233320</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>224683</t>
+          <t>198641</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1024458</t>
+          <t>271654</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>211556</t>
+          <t>242703</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>184339</t>
+          <t>216045</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>240820</t>
+          <t>270603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>667715</t>
+          <t>476023</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>427884</t>
+          <t>430494</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1330652</t>
+          <t>521633</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>29767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>49859</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>74068</t>
+          <t>84200</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50834</t>
+          <t>67036</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>104547</t>
+          <t>106136</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>59756</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>47451</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>78916</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,27 +3749,27 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>132178</t>
+          <t>143955</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>103950</t>
+          <t>121775</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>171654</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1676552</t>
+          <t>1856456</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1187141</t>
+          <t>1810686</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1884601</t>
+          <t>1898698</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1705215</t>
+          <t>1803249</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1665455</t>
+          <t>1764351</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1756033</t>
+          <t>1837126</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3381767</t>
+          <t>3659705</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2806577</t>
+          <t>3601096</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3599820</t>
+          <t>3717623</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>165617</t>
+          <t>175029</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>116058</t>
+          <t>150217</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>201349</t>
+          <t>204818</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>178385</t>
+          <t>198524</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>152412</t>
+          <t>177864</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>203517</t>
+          <t>225848</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>344002</t>
+          <t>373553</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>284619</t>
+          <t>337173</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>390844</t>
+          <t>410293</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
